--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -11,58 +11,22 @@
     <x:sheet name="February 2026" sheetId="9" r:id="rId9"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station License (NEW)</x:t>
@@ -243,7 +207,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -270,12 +234,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -283,6 +241,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -300,13 +279,6 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
@@ -320,6 +292,14 @@
       <x:sz val="14"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -345,15 +325,15 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="17">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -365,14 +345,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -553,8 +533,59 @@
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thick">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thick">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -565,193 +596,246 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="14" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="15" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="16" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1015,509 +1099,485 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45877.1309490741</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>45877.1309606481</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1346451</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>45877.1897222222</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
         <x:v>45897.2409837963</x:v>
       </x:c>
-      <x:c r="I7" s="14">
+      <x:c r="I7" s="18">
         <x:v>45681</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="16" t="n">
         <x:v>1346493</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="K7" s="19" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="17">
         <x:v>45897.2777430556</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="20" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E8" s="20" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="20" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="21">
         <x:v>45880.1214814815</x:v>
       </x:c>
-      <x:c r="I8" s="18">
+      <x:c r="I8" s="22">
         <x:v>45882</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="n">
+      <x:c r="J8" s="20" t="n">
         <x:v>1346457</x:v>
       </x:c>
-      <x:c r="K8" s="19" t="n">
+      <x:c r="K8" s="23" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L8" s="21">
         <x:v>45881.1618981482</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="20" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="B9" s="20" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E9" s="20" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="G9" s="20" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="21">
         <x:v>45881.0630902778</x:v>
       </x:c>
-      <x:c r="I9" s="18">
+      <x:c r="I9" s="22">
         <x:v>45885</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="n">
+      <x:c r="J9" s="20" t="n">
         <x:v>1346453</x:v>
       </x:c>
-      <x:c r="K9" s="19" t="n">
+      <x:c r="K9" s="23" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L9" s="21">
         <x:v>45881.0887037037</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="20" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="B10" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
         <x:v>45897.2535648148</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="24">
         <x:v>45847</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="12" t="n">
         <x:v>1346494</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="14" t="n">
         <x:v>2490</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="15">
         <x:v>45897.2982407407</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="B11" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
         <x:v>45874.1403125</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="24">
         <x:v>46159</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="12" t="n">
         <x:v>1346447</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="14" t="n">
         <x:v>4230</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="15">
         <x:v>45874.2281365741</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="B12" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
         <x:v>45883.1535763889</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I12" s="24">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="12" t="n">
         <x:v>1346468</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K12" s="14" t="n">
         <x:v>4350</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="15">
         <x:v>45883.2560300926</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M12" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="B13" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
         <x:v>45883.2595717593</x:v>
       </x:c>
-      <x:c r="I13" s="18">
+      <x:c r="I13" s="24">
         <x:v>45101</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="12" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K13" s="14" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L13" s="20">
+      <x:c r="L13" s="15">
         <x:v>45883.2880208333</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M13" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="21" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="23" t="s"/>
+      <x:c r="B16" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="27" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="24" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="s">
-        <x:v>58</x:v>
+      <x:c r="B17" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="s">
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
+      <x:c r="B18" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="32" t="s"/>
+      <x:c r="D18" s="32" t="s"/>
+      <x:c r="E18" s="32" t="s"/>
+      <x:c r="F18" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
+      <x:c r="B19" s="31" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C19" s="32" t="s"/>
+      <x:c r="D19" s="32" t="s"/>
+      <x:c r="E19" s="32" t="s"/>
+      <x:c r="F19" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="27" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="29" t="n">
+      <x:c r="B20" s="31" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="32" t="s"/>
+      <x:c r="D20" s="32" t="s"/>
+      <x:c r="E20" s="32" t="s"/>
+      <x:c r="F20" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="27" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
+      <x:c r="B21" s="31" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C21" s="32" t="s"/>
+      <x:c r="D21" s="32" t="s"/>
+      <x:c r="E21" s="32" t="s"/>
+      <x:c r="F21" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="27" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C22" s="28" t="s"/>
-      <x:c r="D22" s="28" t="s"/>
-      <x:c r="E22" s="28" t="s"/>
-      <x:c r="F22" s="29" t="n">
+      <x:c r="B22" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C22" s="32" t="s"/>
+      <x:c r="D22" s="32" t="s"/>
+      <x:c r="E22" s="32" t="s"/>
+      <x:c r="F22" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="27" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C23" s="28" t="s"/>
-      <x:c r="D23" s="28" t="s"/>
-      <x:c r="E23" s="28" t="s"/>
-      <x:c r="F23" s="29" t="n">
+      <x:c r="B23" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C23" s="32" t="s"/>
+      <x:c r="D23" s="32" t="s"/>
+      <x:c r="E23" s="32" t="s"/>
+      <x:c r="F23" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="27" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C24" s="28" t="s"/>
-      <x:c r="D24" s="28" t="s"/>
-      <x:c r="E24" s="28" t="s"/>
-      <x:c r="F24" s="29" t="n">
+      <x:c r="B24" s="31" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C24" s="32" t="s"/>
+      <x:c r="D24" s="32" t="s"/>
+      <x:c r="E24" s="32" t="s"/>
+      <x:c r="F24" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="30" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C25" s="31" t="s"/>
-      <x:c r="D25" s="31" t="s"/>
-      <x:c r="E25" s="31" t="s"/>
-      <x:c r="F25" s="32" t="n">
+      <x:c r="B25" s="34" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C25" s="35" t="s"/>
+      <x:c r="D25" s="35" t="s"/>
+      <x:c r="E25" s="35" t="s"/>
+      <x:c r="F25" s="36" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2578,190 +2638,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>31</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45883.0965162037</x:v>
       </x:c>
-      <x:c r="I6" s="14">
+      <x:c r="I6" s="24">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="J6" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
         <x:v>2592.56</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>45930.3001388889</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="37" t="s"/>
+      <x:c r="C7" s="37" t="s"/>
+      <x:c r="D7" s="37" t="s"/>
+      <x:c r="E7" s="37" t="s"/>
+      <x:c r="F7" s="37" t="s"/>
+      <x:c r="G7" s="37" t="s"/>
+      <x:c r="H7" s="37" t="s"/>
+      <x:c r="I7" s="37" t="s"/>
+      <x:c r="J7" s="37" t="s"/>
+      <x:c r="K7" s="37" t="s"/>
+      <x:c r="L7" s="37" t="s"/>
+      <x:c r="M7" s="37" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C9" s="22" t="s"/>
-      <x:c r="D9" s="22" t="s"/>
-      <x:c r="E9" s="23" t="s"/>
-      <x:c r="F9" s="23" t="s"/>
+      <x:c r="B9" s="38" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C9" s="39" t="s"/>
+      <x:c r="D9" s="39" t="s"/>
+      <x:c r="E9" s="40" t="s"/>
+      <x:c r="F9" s="40" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="24" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C10" s="25" t="s"/>
-      <x:c r="D10" s="25" t="s"/>
-      <x:c r="E10" s="25" t="s"/>
-      <x:c r="F10" s="26" t="s">
-        <x:v>58</x:v>
+      <x:c r="B10" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s"/>
+      <x:c r="D10" s="29" t="s"/>
+      <x:c r="E10" s="29" t="s"/>
+      <x:c r="F10" s="30" t="s">
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s"/>
-      <x:c r="D11" s="28" t="s"/>
-      <x:c r="E11" s="28" t="s"/>
-      <x:c r="F11" s="29" t="n">
+      <x:c r="B11" s="31" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C11" s="32" t="s"/>
+      <x:c r="D11" s="32" t="s"/>
+      <x:c r="E11" s="32" t="s"/>
+      <x:c r="F11" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="30" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C12" s="31" t="s"/>
-      <x:c r="D12" s="31" t="s"/>
-      <x:c r="E12" s="31" t="s"/>
-      <x:c r="F12" s="32" t="n">
+      <x:c r="B12" s="34" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C12" s="35" t="s"/>
+      <x:c r="D12" s="35" t="s"/>
+      <x:c r="E12" s="35" t="s"/>
+      <x:c r="F12" s="36" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3829,190 +3885,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>22</x:v>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46062.2741666667</x:v>
       </x:c>
-      <x:c r="I6" s="14">
+      <x:c r="I6" s="24">
         <x:v>46075</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1346991</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46077.1029513889</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="37" t="s"/>
+      <x:c r="C7" s="37" t="s"/>
+      <x:c r="D7" s="37" t="s"/>
+      <x:c r="E7" s="37" t="s"/>
+      <x:c r="F7" s="37" t="s"/>
+      <x:c r="G7" s="37" t="s"/>
+      <x:c r="H7" s="37" t="s"/>
+      <x:c r="I7" s="37" t="s"/>
+      <x:c r="J7" s="37" t="s"/>
+      <x:c r="K7" s="37" t="s"/>
+      <x:c r="L7" s="37" t="s"/>
+      <x:c r="M7" s="37" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C9" s="22" t="s"/>
-      <x:c r="D9" s="22" t="s"/>
-      <x:c r="E9" s="23" t="s"/>
-      <x:c r="F9" s="23" t="s"/>
+      <x:c r="B9" s="38" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C9" s="39" t="s"/>
+      <x:c r="D9" s="39" t="s"/>
+      <x:c r="E9" s="40" t="s"/>
+      <x:c r="F9" s="40" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="24" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C10" s="25" t="s"/>
-      <x:c r="D10" s="25" t="s"/>
-      <x:c r="E10" s="25" t="s"/>
-      <x:c r="F10" s="26" t="s">
-        <x:v>58</x:v>
+      <x:c r="B10" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s"/>
+      <x:c r="D10" s="29" t="s"/>
+      <x:c r="E10" s="29" t="s"/>
+      <x:c r="F10" s="30" t="s">
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s"/>
-      <x:c r="D11" s="28" t="s"/>
-      <x:c r="E11" s="28" t="s"/>
-      <x:c r="F11" s="29" t="n">
+      <x:c r="B11" s="31" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C11" s="32" t="s"/>
+      <x:c r="D11" s="32" t="s"/>
+      <x:c r="E11" s="32" t="s"/>
+      <x:c r="F11" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="30" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C12" s="31" t="s"/>
-      <x:c r="D12" s="31" t="s"/>
-      <x:c r="E12" s="31" t="s"/>
-      <x:c r="F12" s="32" t="n">
+      <x:c r="B12" s="34" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C12" s="35" t="s"/>
+      <x:c r="D12" s="35" t="s"/>
+      <x:c r="E12" s="35" t="s"/>
+      <x:c r="F12" s="36" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -24,9 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
-  <x:si>
-    <x:t>{{Name}}</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+  <x:si>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA. ANNA SOMOZA</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station License (NEW)</x:t>
@@ -207,7 +210,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -294,14 +297,6 @@
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="18"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
   </x:fonts>
   <x:fills count="5">
     <x:fill>
@@ -325,7 +320,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="17">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -533,59 +528,8 @@
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="thick">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thick">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="33">
+  <x:cellStyleXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -674,17 +618,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="14" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="15" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="16" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -720,6 +655,58 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -731,6 +718,10 @@
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -739,40 +730,8 @@
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -823,20 +782,16 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1084,7 +1039,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -1101,7 +1058,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45870</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -1162,24 +1119,24 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>45877.1309490741</x:v>
@@ -1197,30 +1154,30 @@
         <x:v>45877.1897222222</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D7" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E7" s="16" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G7" s="16" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="17">
         <x:v>45897.2409837963</x:v>
@@ -1238,29 +1195,29 @@
         <x:v>45897.2777430556</x:v>
       </x:c>
       <x:c r="M7" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="20" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="20" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D8" s="20" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E8" s="20" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="20" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G8" s="20" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="21">
         <x:v>45880.1214814815</x:v>
@@ -1278,27 +1235,27 @@
         <x:v>45881.1618981482</x:v>
       </x:c>
       <x:c r="M8" s="20" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="20" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="20" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="20" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="20" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="20" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G9" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H9" s="21">
         <x:v>45881.0630902778</x:v>
@@ -1316,273 +1273,299 @@
         <x:v>45881.0887037037</x:v>
       </x:c>
       <x:c r="M9" s="20" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="B10" s="24" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="24" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="D10" s="25" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E10" s="24" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="F10" s="24" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="G10" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="26">
         <x:v>45897.2535648148</x:v>
       </x:c>
-      <x:c r="I10" s="24">
+      <x:c r="I10" s="27">
         <x:v>45847</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="25" t="n">
         <x:v>1346494</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="28" t="n">
         <x:v>2490</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="29">
         <x:v>45897.2982407407</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M10" s="24" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="s">
+      <x:c r="B11" s="24" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="s">
+      <x:c r="C11" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="D11" s="25" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="E11" s="24" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="F11" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="G11" s="24" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H11" s="26">
         <x:v>45874.1403125</x:v>
       </x:c>
-      <x:c r="I11" s="24">
+      <x:c r="I11" s="27">
         <x:v>46159</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="25" t="n">
         <x:v>1346447</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="K11" s="28" t="n">
         <x:v>4230</x:v>
       </x:c>
-      <x:c r="L11" s="15">
+      <x:c r="L11" s="29">
         <x:v>45874.2281365741</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M11" s="24" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="s">
+      <x:c r="B12" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="s">
+      <x:c r="C12" s="24" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="s">
+      <x:c r="D12" s="25" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E12" s="24" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="s">
+      <x:c r="F12" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H12" s="13">
+      <x:c r="G12" s="24" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H12" s="26">
         <x:v>45883.1535763889</x:v>
       </x:c>
-      <x:c r="I12" s="24">
+      <x:c r="I12" s="27">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="n">
+      <x:c r="J12" s="25" t="n">
         <x:v>1346468</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="n">
+      <x:c r="K12" s="28" t="n">
         <x:v>4350</x:v>
       </x:c>
-      <x:c r="L12" s="15">
+      <x:c r="L12" s="29">
         <x:v>45883.2560300926</x:v>
       </x:c>
-      <x:c r="M12" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M12" s="24" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="s">
+      <x:c r="C13" s="24" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="s">
+      <x:c r="D13" s="25" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E13" s="24" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="s">
+      <x:c r="F13" s="24" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H13" s="13">
+      <x:c r="G13" s="24" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H13" s="26">
         <x:v>45883.2595717593</x:v>
       </x:c>
-      <x:c r="I13" s="24">
+      <x:c r="I13" s="27">
         <x:v>45101</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="n">
+      <x:c r="J13" s="25" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="n">
+      <x:c r="K13" s="28" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L13" s="15">
+      <x:c r="L13" s="29">
         <x:v>45883.2880208333</x:v>
       </x:c>
-      <x:c r="M13" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M13" s="24" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="27" t="s"/>
+    <x:row r="14" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B14" s="30" t="s"/>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="30" t="s"/>
+      <x:c r="G14" s="30" t="s"/>
+      <x:c r="H14" s="30" t="s"/>
+      <x:c r="I14" s="30" t="s"/>
+      <x:c r="J14" s="30" t="s"/>
+      <x:c r="K14" s="30" t="s"/>
+      <x:c r="L14" s="30" t="s"/>
+      <x:c r="M14" s="30" t="s"/>
     </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="28" t="s">
+    <x:row r="15" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B15" s="30" t="s"/>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="30" t="s"/>
+      <x:c r="G15" s="30" t="s"/>
+      <x:c r="H15" s="30" t="s"/>
+      <x:c r="I15" s="30" t="s"/>
+      <x:c r="J15" s="30" t="s"/>
+      <x:c r="K15" s="30" t="s"/>
+      <x:c r="L15" s="30" t="s"/>
+      <x:c r="M15" s="30" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="31" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="31" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="C18" s="32" t="s"/>
       <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="E18" s="33" t="s"/>
+      <x:c r="F18" s="33" t="s"/>
     </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="31" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C19" s="32" t="s"/>
-      <x:c r="D19" s="32" t="s"/>
-      <x:c r="E19" s="32" t="s"/>
-      <x:c r="F19" s="33" t="n">
-        <x:v>1</x:v>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="34" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C19" s="35" t="s"/>
+      <x:c r="D19" s="35" t="s"/>
+      <x:c r="E19" s="35" t="s"/>
+      <x:c r="F19" s="36" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="31" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C20" s="32" t="s"/>
-      <x:c r="D20" s="32" t="s"/>
-      <x:c r="E20" s="32" t="s"/>
-      <x:c r="F20" s="33" t="n">
+      <x:c r="B20" s="37" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C20" s="38" t="s"/>
+      <x:c r="D20" s="38" t="s"/>
+      <x:c r="E20" s="38" t="s"/>
+      <x:c r="F20" s="39" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="31" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C21" s="32" t="s"/>
-      <x:c r="D21" s="32" t="s"/>
-      <x:c r="E21" s="32" t="s"/>
-      <x:c r="F21" s="33" t="n">
-        <x:v>2</x:v>
+      <x:c r="B21" s="37" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C21" s="38" t="s"/>
+      <x:c r="D21" s="38" t="s"/>
+      <x:c r="E21" s="38" t="s"/>
+      <x:c r="F21" s="39" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C22" s="32" t="s"/>
-      <x:c r="D22" s="32" t="s"/>
-      <x:c r="E22" s="32" t="s"/>
-      <x:c r="F22" s="33" t="n">
+      <x:c r="B22" s="37" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C22" s="38" t="s"/>
+      <x:c r="D22" s="38" t="s"/>
+      <x:c r="E22" s="38" t="s"/>
+      <x:c r="F22" s="39" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="31" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C23" s="32" t="s"/>
-      <x:c r="D23" s="32" t="s"/>
-      <x:c r="E23" s="32" t="s"/>
-      <x:c r="F23" s="33" t="n">
-        <x:v>1</x:v>
+      <x:c r="B23" s="37" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C23" s="38" t="s"/>
+      <x:c r="D23" s="38" t="s"/>
+      <x:c r="E23" s="38" t="s"/>
+      <x:c r="F23" s="39" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="31" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C24" s="32" t="s"/>
-      <x:c r="D24" s="32" t="s"/>
-      <x:c r="E24" s="32" t="s"/>
-      <x:c r="F24" s="33" t="n">
+      <x:c r="B24" s="37" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C24" s="38" t="s"/>
+      <x:c r="D24" s="38" t="s"/>
+      <x:c r="E24" s="38" t="s"/>
+      <x:c r="F24" s="39" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="34" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C25" s="35" t="s"/>
-      <x:c r="D25" s="35" t="s"/>
-      <x:c r="E25" s="35" t="s"/>
-      <x:c r="F25" s="36" t="n">
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="37" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C25" s="38" t="s"/>
+      <x:c r="D25" s="38" t="s"/>
+      <x:c r="E25" s="38" t="s"/>
+      <x:c r="F25" s="39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="37" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C26" s="38" t="s"/>
+      <x:c r="D26" s="38" t="s"/>
+      <x:c r="E26" s="38" t="s"/>
+      <x:c r="F26" s="39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="40" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C27" s="41" t="s"/>
+      <x:c r="D27" s="41" t="s"/>
+      <x:c r="E27" s="41" t="s"/>
+      <x:c r="F27" s="42" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2550,12 +2533,11 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="12">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+  <x:mergeCells count="13">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
@@ -2563,6 +2545,8 @@
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2623,7 +2607,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -2640,7 +2626,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45901</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -2701,33 +2687,33 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>45883.0965162037</x:v>
       </x:c>
-      <x:c r="I6" s="24">
+      <x:c r="I6" s="43">
         <x:v>45839</x:v>
       </x:c>
       <x:c r="J6" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K6" s="14" t="n">
         <x:v>2592.56</x:v>
@@ -2736,50 +2722,48 @@
         <x:v>45930.3001388889</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="37" t="s"/>
-      <x:c r="C7" s="37" t="s"/>
-      <x:c r="D7" s="37" t="s"/>
-      <x:c r="E7" s="37" t="s"/>
-      <x:c r="F7" s="37" t="s"/>
-      <x:c r="G7" s="37" t="s"/>
-      <x:c r="H7" s="37" t="s"/>
-      <x:c r="I7" s="37" t="s"/>
-      <x:c r="J7" s="37" t="s"/>
-      <x:c r="K7" s="37" t="s"/>
-      <x:c r="L7" s="37" t="s"/>
-      <x:c r="M7" s="37" t="s"/>
+      <x:c r="B7" s="44" t="s"/>
+      <x:c r="C7" s="44" t="s"/>
+      <x:c r="D7" s="44" t="s"/>
+      <x:c r="E7" s="44" t="s"/>
+      <x:c r="F7" s="44" t="s"/>
+      <x:c r="G7" s="44" t="s"/>
+      <x:c r="H7" s="44" t="s"/>
+      <x:c r="I7" s="44" t="s"/>
+      <x:c r="J7" s="44" t="s"/>
+      <x:c r="K7" s="44" t="s"/>
+      <x:c r="L7" s="44" t="s"/>
+      <x:c r="M7" s="44" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="45" t="s"/>
+      <x:c r="C8" s="45" t="s"/>
+      <x:c r="D8" s="45" t="s"/>
+      <x:c r="E8" s="45" t="s"/>
+      <x:c r="F8" s="45" t="s"/>
+      <x:c r="G8" s="45" t="s"/>
+      <x:c r="H8" s="45" t="s"/>
+      <x:c r="I8" s="45" t="s"/>
+      <x:c r="J8" s="45" t="s"/>
+      <x:c r="K8" s="45" t="s"/>
+      <x:c r="L8" s="45" t="s"/>
+      <x:c r="M8" s="45" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="38" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C9" s="39" t="s"/>
-      <x:c r="D9" s="39" t="s"/>
-      <x:c r="E9" s="40" t="s"/>
-      <x:c r="F9" s="40" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -2788,41 +2772,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="28" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="31" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s"/>
-      <x:c r="D10" s="29" t="s"/>
-      <x:c r="E10" s="29" t="s"/>
-      <x:c r="F10" s="30" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="31" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="32" t="s"/>
       <x:c r="D11" s="32" t="s"/>
-      <x:c r="E11" s="32" t="s"/>
-      <x:c r="F11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="E11" s="33" t="s"/>
+      <x:c r="F11" s="33" t="s"/>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="34" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C12" s="35" t="s"/>
       <x:c r="D12" s="35" t="s"/>
       <x:c r="E12" s="35" t="s"/>
-      <x:c r="F12" s="36" t="n">
+      <x:c r="F12" s="36" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="37" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C13" s="38" t="s"/>
+      <x:c r="D13" s="38" t="s"/>
+      <x:c r="E13" s="38" t="s"/>
+      <x:c r="F13" s="39" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="40" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C14" s="41" t="s"/>
+      <x:c r="D14" s="41" t="s"/>
+      <x:c r="E14" s="41" t="s"/>
+      <x:c r="F14" s="42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3803,13 +3795,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3870,7 +3863,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -3887,7 +3882,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46054</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -3948,29 +3943,29 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46062.2741666667</x:v>
       </x:c>
-      <x:c r="I6" s="24">
+      <x:c r="I6" s="43">
         <x:v>46075</x:v>
       </x:c>
       <x:c r="J6" s="12" t="n">
@@ -3983,50 +3978,48 @@
         <x:v>46077.1029513889</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="37" t="s"/>
-      <x:c r="C7" s="37" t="s"/>
-      <x:c r="D7" s="37" t="s"/>
-      <x:c r="E7" s="37" t="s"/>
-      <x:c r="F7" s="37" t="s"/>
-      <x:c r="G7" s="37" t="s"/>
-      <x:c r="H7" s="37" t="s"/>
-      <x:c r="I7" s="37" t="s"/>
-      <x:c r="J7" s="37" t="s"/>
-      <x:c r="K7" s="37" t="s"/>
-      <x:c r="L7" s="37" t="s"/>
-      <x:c r="M7" s="37" t="s"/>
+      <x:c r="B7" s="44" t="s"/>
+      <x:c r="C7" s="44" t="s"/>
+      <x:c r="D7" s="44" t="s"/>
+      <x:c r="E7" s="44" t="s"/>
+      <x:c r="F7" s="44" t="s"/>
+      <x:c r="G7" s="44" t="s"/>
+      <x:c r="H7" s="44" t="s"/>
+      <x:c r="I7" s="44" t="s"/>
+      <x:c r="J7" s="44" t="s"/>
+      <x:c r="K7" s="44" t="s"/>
+      <x:c r="L7" s="44" t="s"/>
+      <x:c r="M7" s="44" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="45" t="s"/>
+      <x:c r="C8" s="45" t="s"/>
+      <x:c r="D8" s="45" t="s"/>
+      <x:c r="E8" s="45" t="s"/>
+      <x:c r="F8" s="45" t="s"/>
+      <x:c r="G8" s="45" t="s"/>
+      <x:c r="H8" s="45" t="s"/>
+      <x:c r="I8" s="45" t="s"/>
+      <x:c r="J8" s="45" t="s"/>
+      <x:c r="K8" s="45" t="s"/>
+      <x:c r="L8" s="45" t="s"/>
+      <x:c r="M8" s="45" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="38" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C9" s="39" t="s"/>
-      <x:c r="D9" s="39" t="s"/>
-      <x:c r="E9" s="40" t="s"/>
-      <x:c r="F9" s="40" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -4035,41 +4028,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="28" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="31" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s"/>
-      <x:c r="D10" s="29" t="s"/>
-      <x:c r="E10" s="29" t="s"/>
-      <x:c r="F10" s="30" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="31" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="C11" s="32" t="s"/>
       <x:c r="D11" s="32" t="s"/>
-      <x:c r="E11" s="32" t="s"/>
-      <x:c r="F11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="E11" s="33" t="s"/>
+      <x:c r="F11" s="33" t="s"/>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="34" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C12" s="35" t="s"/>
       <x:c r="D12" s="35" t="s"/>
       <x:c r="E12" s="35" t="s"/>
-      <x:c r="F12" s="36" t="n">
+      <x:c r="F12" s="36" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="37" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C13" s="38" t="s"/>
+      <x:c r="D13" s="38" t="s"/>
+      <x:c r="E13" s="38" t="s"/>
+      <x:c r="F13" s="39" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="40" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C14" s="41" t="s"/>
+      <x:c r="D14" s="41" t="s"/>
+      <x:c r="E14" s="41" t="s"/>
+      <x:c r="F14" s="42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5050,13 +5051,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -1089,7 +1089,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1159,7 +1159,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>9</x:v>
@@ -2657,7 +2657,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -2727,7 +2727,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="44" t="s"/>
       <x:c r="C7" s="44" t="s"/>
@@ -3913,7 +3913,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3983,7 +3983,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="44" t="s"/>
       <x:c r="C7" s="44" t="s"/>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -24,12 +24,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>MA. ANNA SOMOZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station License (NEW)</x:t>
@@ -210,7 +246,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -255,21 +291,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -279,6 +300,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -529,7 +557,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -540,86 +568,74 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -650,64 +666,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -718,80 +678,84 @@
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1091,18 +1055,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1120,449 +1072,461 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45877.1309490741</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45877.1309606481</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1346451</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45877.1897222222</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="L7" s="10" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="M7" s="10" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45897.2409837963</x:v>
-      </x:c>
-      <x:c r="I7" s="18">
-        <x:v>45681</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1346493</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>45897.2777430556</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>8</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="20" t="s">
+      <x:c r="B8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="20" t="s">
+      <x:c r="D8" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="20" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E8" s="20" t="s">
+      <x:c r="E8" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="20" t="s">
+      <x:c r="F8" s="11" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="20" t="s">
+      <x:c r="G8" s="11" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="21">
-        <x:v>45880.1214814815</x:v>
-      </x:c>
-      <x:c r="I8" s="22">
-        <x:v>45882</x:v>
-      </x:c>
-      <x:c r="J8" s="20" t="n">
-        <x:v>1346457</x:v>
-      </x:c>
-      <x:c r="K8" s="23" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L8" s="21">
-        <x:v>45881.1618981482</x:v>
-      </x:c>
-      <x:c r="M8" s="20" t="s">
-        <x:v>8</x:v>
+      <x:c r="H8" s="12">
+        <x:v>45877.1309490741</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45877.1309606481</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1346451</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45877.1897222222</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="20" t="s">
+      <x:c r="B9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45897.2409837963</x:v>
+      </x:c>
+      <x:c r="I9" s="14">
+        <x:v>45681</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1346493</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45897.2777430556</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="20" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="20" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E9" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="20" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="21">
-        <x:v>45881.0630902778</x:v>
-      </x:c>
-      <x:c r="I9" s="22">
-        <x:v>45885</x:v>
-      </x:c>
-      <x:c r="J9" s="20" t="n">
-        <x:v>1346453</x:v>
-      </x:c>
-      <x:c r="K9" s="23" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L9" s="21">
-        <x:v>45881.0887037037</x:v>
-      </x:c>
-      <x:c r="M9" s="20" t="s">
-        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="24" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>45880.1214814815</x:v>
+      </x:c>
+      <x:c r="I10" s="18">
+        <x:v>45882</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>1346457</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L10" s="20">
+        <x:v>45881.1618981482</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="C10" s="24" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="25" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E10" s="24" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="24" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H10" s="26">
-        <x:v>45897.2535648148</x:v>
-      </x:c>
-      <x:c r="I10" s="27">
-        <x:v>45847</x:v>
-      </x:c>
-      <x:c r="J10" s="25" t="n">
-        <x:v>1346494</x:v>
-      </x:c>
-      <x:c r="K10" s="28" t="n">
-        <x:v>2490</x:v>
-      </x:c>
-      <x:c r="L10" s="29">
-        <x:v>45897.2982407407</x:v>
-      </x:c>
-      <x:c r="M10" s="24" t="s">
-        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="24" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C11" s="24" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="25" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E11" s="24" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F11" s="24" t="s">
+      <x:c r="C11" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G11" s="24" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H11" s="26">
-        <x:v>45874.1403125</x:v>
-      </x:c>
-      <x:c r="I11" s="27">
-        <x:v>46159</x:v>
-      </x:c>
-      <x:c r="J11" s="25" t="n">
-        <x:v>1346447</x:v>
-      </x:c>
-      <x:c r="K11" s="28" t="n">
-        <x:v>4230</x:v>
-      </x:c>
-      <x:c r="L11" s="29">
-        <x:v>45874.2281365741</x:v>
-      </x:c>
-      <x:c r="M11" s="24" t="s">
-        <x:v>8</x:v>
+      <x:c r="F11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45881.0630902778</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>45885</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1346453</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L11" s="20">
+        <x:v>45881.0887037037</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D12" s="25" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E12" s="24" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F12" s="24" t="s">
+      <x:c r="D12" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G12" s="24" t="s">
+      <x:c r="F12" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H12" s="26">
-        <x:v>45883.1535763889</x:v>
-      </x:c>
-      <x:c r="I12" s="27">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J12" s="25" t="n">
-        <x:v>1346468</x:v>
-      </x:c>
-      <x:c r="K12" s="28" t="n">
-        <x:v>4350</x:v>
-      </x:c>
-      <x:c r="L12" s="29">
-        <x:v>45883.2560300926</x:v>
-      </x:c>
-      <x:c r="M12" s="24" t="s">
-        <x:v>8</x:v>
+      <x:c r="G12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45897.2535648148</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>45847</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1346494</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
+        <x:v>2490</x:v>
+      </x:c>
+      <x:c r="L12" s="20">
+        <x:v>45897.2982407407</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s">
+      <x:c r="B13" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D13" s="25" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E13" s="24" t="s">
+      <x:c r="C13" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F13" s="24" t="s">
+      <x:c r="D13" s="16" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G13" s="24" t="s">
+      <x:c r="E13" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H13" s="26">
+      <x:c r="F13" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>45874.1403125</x:v>
+      </x:c>
+      <x:c r="I13" s="18">
+        <x:v>46159</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1346447</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="n">
+        <x:v>4230</x:v>
+      </x:c>
+      <x:c r="L13" s="20">
+        <x:v>45874.2281365741</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>45883.1535763889</x:v>
+      </x:c>
+      <x:c r="I14" s="18">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1346468</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="n">
+        <x:v>4350</x:v>
+      </x:c>
+      <x:c r="L14" s="20">
+        <x:v>45883.2560300926</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
         <x:v>45883.2595717593</x:v>
       </x:c>
-      <x:c r="I13" s="27">
+      <x:c r="I15" s="18">
         <x:v>45101</x:v>
       </x:c>
-      <x:c r="J13" s="25" t="n">
+      <x:c r="J15" s="16" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K13" s="28" t="n">
+      <x:c r="K15" s="19" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L13" s="29">
+      <x:c r="L15" s="20">
         <x:v>45883.2880208333</x:v>
       </x:c>
-      <x:c r="M13" s="24" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B14" s="30" t="s"/>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="30" t="s"/>
-      <x:c r="G14" s="30" t="s"/>
-      <x:c r="H14" s="30" t="s"/>
-      <x:c r="I14" s="30" t="s"/>
-      <x:c r="J14" s="30" t="s"/>
-      <x:c r="K14" s="30" t="s"/>
-      <x:c r="L14" s="30" t="s"/>
-      <x:c r="M14" s="30" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B15" s="30" t="s"/>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="30" t="s"/>
-      <x:c r="G15" s="30" t="s"/>
-      <x:c r="H15" s="30" t="s"/>
-      <x:c r="I15" s="30" t="s"/>
-      <x:c r="J15" s="30" t="s"/>
-      <x:c r="K15" s="30" t="s"/>
-      <x:c r="L15" s="30" t="s"/>
-      <x:c r="M15" s="30" t="s"/>
+      <x:c r="M15" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="31" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C18" s="32" t="s"/>
-      <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="33" t="s"/>
-      <x:c r="F18" s="33" t="s"/>
+      <x:c r="B18" s="21" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="23" t="s"/>
+      <x:c r="F18" s="23" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="34" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C19" s="35" t="s"/>
-      <x:c r="D19" s="35" t="s"/>
-      <x:c r="E19" s="35" t="s"/>
-      <x:c r="F19" s="36" t="s">
-        <x:v>47</x:v>
+      <x:c r="B19" s="24" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="37" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="38" t="s"/>
-      <x:c r="D20" s="38" t="s"/>
-      <x:c r="E20" s="38" t="s"/>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="B20" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="37" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C21" s="38" t="s"/>
-      <x:c r="D21" s="38" t="s"/>
-      <x:c r="E21" s="38" t="s"/>
-      <x:c r="F21" s="39" t="n">
+      <x:c r="B21" s="27" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="37" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C22" s="38" t="s"/>
-      <x:c r="D22" s="38" t="s"/>
-      <x:c r="E22" s="38" t="s"/>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="B22" s="27" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="s"/>
+      <x:c r="D22" s="28" t="s"/>
+      <x:c r="E22" s="28" t="s"/>
+      <x:c r="F22" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="37" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C23" s="38" t="s"/>
-      <x:c r="D23" s="38" t="s"/>
-      <x:c r="E23" s="38" t="s"/>
-      <x:c r="F23" s="39" t="n">
+      <x:c r="B23" s="27" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C23" s="28" t="s"/>
+      <x:c r="D23" s="28" t="s"/>
+      <x:c r="E23" s="28" t="s"/>
+      <x:c r="F23" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="37" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C24" s="38" t="s"/>
-      <x:c r="D24" s="38" t="s"/>
-      <x:c r="E24" s="38" t="s"/>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="B24" s="27" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C24" s="28" t="s"/>
+      <x:c r="D24" s="28" t="s"/>
+      <x:c r="E24" s="28" t="s"/>
+      <x:c r="F24" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="37" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C25" s="38" t="s"/>
-      <x:c r="D25" s="38" t="s"/>
-      <x:c r="E25" s="38" t="s"/>
-      <x:c r="F25" s="39" t="n">
+      <x:c r="B25" s="27" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C25" s="28" t="s"/>
+      <x:c r="D25" s="28" t="s"/>
+      <x:c r="E25" s="28" t="s"/>
+      <x:c r="F25" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="37" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C26" s="38" t="s"/>
-      <x:c r="D26" s="38" t="s"/>
-      <x:c r="E26" s="38" t="s"/>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="B26" s="27" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C26" s="28" t="s"/>
+      <x:c r="D26" s="28" t="s"/>
+      <x:c r="E26" s="28" t="s"/>
+      <x:c r="F26" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="40" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C27" s="41" t="s"/>
-      <x:c r="D27" s="41" t="s"/>
-      <x:c r="E27" s="41" t="s"/>
-      <x:c r="F27" s="42" t="n">
+      <x:c r="B27" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C27" s="31" t="s"/>
+      <x:c r="D27" s="31" t="s"/>
+      <x:c r="E27" s="31" t="s"/>
+      <x:c r="F27" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2659,18 +2623,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2688,75 +2640,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45883.0965162037</x:v>
-      </x:c>
-      <x:c r="I6" s="43">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>2592.56</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45930.3001388889</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="44" t="s"/>
-      <x:c r="C7" s="44" t="s"/>
-      <x:c r="D7" s="44" t="s"/>
-      <x:c r="E7" s="44" t="s"/>
-      <x:c r="F7" s="44" t="s"/>
-      <x:c r="G7" s="44" t="s"/>
-      <x:c r="H7" s="44" t="s"/>
-      <x:c r="I7" s="44" t="s"/>
-      <x:c r="J7" s="44" t="s"/>
-      <x:c r="K7" s="44" t="s"/>
-      <x:c r="L7" s="44" t="s"/>
-      <x:c r="M7" s="44" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="45" t="s"/>
-      <x:c r="C8" s="45" t="s"/>
-      <x:c r="D8" s="45" t="s"/>
-      <x:c r="E8" s="45" t="s"/>
-      <x:c r="F8" s="45" t="s"/>
-      <x:c r="G8" s="45" t="s"/>
-      <x:c r="H8" s="45" t="s"/>
-      <x:c r="I8" s="45" t="s"/>
-      <x:c r="J8" s="45" t="s"/>
-      <x:c r="K8" s="45" t="s"/>
-      <x:c r="L8" s="45" t="s"/>
-      <x:c r="M8" s="45" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45883.0965162037</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>2592.56</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45930.3001388889</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -2774,44 +2738,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="31" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C11" s="32" t="s"/>
-      <x:c r="D11" s="32" t="s"/>
-      <x:c r="E11" s="33" t="s"/>
-      <x:c r="F11" s="33" t="s"/>
+      <x:c r="B11" s="21" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="23" t="s"/>
+      <x:c r="F11" s="23" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="34" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C12" s="35" t="s"/>
-      <x:c r="D12" s="35" t="s"/>
-      <x:c r="E12" s="35" t="s"/>
-      <x:c r="F12" s="36" t="s">
-        <x:v>47</x:v>
+      <x:c r="B12" s="24" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="37" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="38" t="s"/>
-      <x:c r="D13" s="38" t="s"/>
-      <x:c r="E13" s="38" t="s"/>
-      <x:c r="F13" s="39" t="n">
+      <x:c r="B13" s="27" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="28" t="s"/>
+      <x:c r="D13" s="28" t="s"/>
+      <x:c r="E13" s="28" t="s"/>
+      <x:c r="F13" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="40" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C14" s="41" t="s"/>
-      <x:c r="D14" s="41" t="s"/>
-      <x:c r="E14" s="41" t="s"/>
-      <x:c r="F14" s="42" t="n">
+      <x:c r="B14" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C14" s="31" t="s"/>
+      <x:c r="D14" s="31" t="s"/>
+      <x:c r="E14" s="31" t="s"/>
+      <x:c r="F14" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3915,18 +3879,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3944,75 +3896,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46062.2741666667</x:v>
-      </x:c>
-      <x:c r="I6" s="43">
-        <x:v>46075</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46077.1029513889</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="44" t="s"/>
-      <x:c r="C7" s="44" t="s"/>
-      <x:c r="D7" s="44" t="s"/>
-      <x:c r="E7" s="44" t="s"/>
-      <x:c r="F7" s="44" t="s"/>
-      <x:c r="G7" s="44" t="s"/>
-      <x:c r="H7" s="44" t="s"/>
-      <x:c r="I7" s="44" t="s"/>
-      <x:c r="J7" s="44" t="s"/>
-      <x:c r="K7" s="44" t="s"/>
-      <x:c r="L7" s="44" t="s"/>
-      <x:c r="M7" s="44" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="45" t="s"/>
-      <x:c r="C8" s="45" t="s"/>
-      <x:c r="D8" s="45" t="s"/>
-      <x:c r="E8" s="45" t="s"/>
-      <x:c r="F8" s="45" t="s"/>
-      <x:c r="G8" s="45" t="s"/>
-      <x:c r="H8" s="45" t="s"/>
-      <x:c r="I8" s="45" t="s"/>
-      <x:c r="J8" s="45" t="s"/>
-      <x:c r="K8" s="45" t="s"/>
-      <x:c r="L8" s="45" t="s"/>
-      <x:c r="M8" s="45" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46062.2741666667</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>46075</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46077.1029513889</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -4030,44 +3994,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="31" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C11" s="32" t="s"/>
-      <x:c r="D11" s="32" t="s"/>
-      <x:c r="E11" s="33" t="s"/>
-      <x:c r="F11" s="33" t="s"/>
+      <x:c r="B11" s="21" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="23" t="s"/>
+      <x:c r="F11" s="23" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="34" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C12" s="35" t="s"/>
-      <x:c r="D12" s="35" t="s"/>
-      <x:c r="E12" s="35" t="s"/>
-      <x:c r="F12" s="36" t="s">
-        <x:v>47</x:v>
+      <x:c r="B12" s="24" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="37" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C13" s="38" t="s"/>
-      <x:c r="D13" s="38" t="s"/>
-      <x:c r="E13" s="38" t="s"/>
-      <x:c r="F13" s="39" t="n">
+      <x:c r="B13" s="27" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C13" s="28" t="s"/>
+      <x:c r="D13" s="28" t="s"/>
+      <x:c r="E13" s="28" t="s"/>
+      <x:c r="F13" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="40" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C14" s="41" t="s"/>
-      <x:c r="D14" s="41" t="s"/>
-      <x:c r="E14" s="41" t="s"/>
-      <x:c r="F14" s="42" t="n">
+      <x:c r="B14" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C14" s="31" t="s"/>
+      <x:c r="D14" s="31" t="s"/>
+      <x:c r="E14" s="31" t="s"/>
+      <x:c r="F14" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -32,6 +32,9 @@
     <x:t>MA. ANNA SOMOZA</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | August 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -209,6 +212,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | September 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>PETRON CORPORATION - ZAMBOANGA TERMINAL</x:t>
   </x:si>
   <x:si>
@@ -222,6 +228,9 @@
   </x:si>
   <x:si>
     <x:t>1346650/1346651/1346652</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | February 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -246,7 +255,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -286,6 +295,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -557,14 +590,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -577,65 +619,65 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -666,95 +708,107 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -983,58 +1037,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1077,456 +1131,456 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45877.1309490741</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>45877.1309606481</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1346451</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45877.1897222222</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45897.2409837963</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45681</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346493</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45897.2777430556</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
-        <x:v>45897.2409837963</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45681</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>1346493</x:v>
-      </x:c>
-      <x:c r="K9" s="13" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L9" s="12">
-        <x:v>45897.2777430556</x:v>
-      </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="B10" s="18" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="C10" s="18" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="D10" s="19" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="F10" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="G10" s="18" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>45880.1214814815</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="21">
         <x:v>45882</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1346457</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="23">
         <x:v>45881.1618981482</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="C11" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="D11" s="19" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="F11" s="18" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="G11" s="18" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>45881.0630902778</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="21">
         <x:v>45885</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1346453</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="23">
         <x:v>45881.0887037037</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="B12" s="18" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="D12" s="19" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="F12" s="18" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="G12" s="18" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H12" s="20">
         <x:v>45897.2535648148</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I12" s="21">
         <x:v>45847</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="19" t="n">
         <x:v>1346494</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K12" s="22" t="n">
         <x:v>2490</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="23">
         <x:v>45897.2982407407</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M12" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="B13" s="18" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="C13" s="18" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="D13" s="19" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="E13" s="18" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="F13" s="18" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="G13" s="18" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H13" s="20">
         <x:v>45874.1403125</x:v>
       </x:c>
-      <x:c r="I13" s="18">
+      <x:c r="I13" s="21">
         <x:v>46159</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="19" t="n">
         <x:v>1346447</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K13" s="22" t="n">
         <x:v>4230</x:v>
       </x:c>
-      <x:c r="L13" s="20">
+      <x:c r="L13" s="23">
         <x:v>45874.2281365741</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M13" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="B14" s="18" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="C14" s="18" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="D14" s="19" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="F14" s="18" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="G14" s="18" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H14" s="20">
         <x:v>45883.1535763889</x:v>
       </x:c>
-      <x:c r="I14" s="18">
+      <x:c r="I14" s="21">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="n">
+      <x:c r="J14" s="19" t="n">
         <x:v>1346468</x:v>
       </x:c>
-      <x:c r="K14" s="19" t="n">
+      <x:c r="K14" s="22" t="n">
         <x:v>4350</x:v>
       </x:c>
-      <x:c r="L14" s="20">
+      <x:c r="L14" s="23">
         <x:v>45883.2560300926</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M14" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="B15" s="18" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="C15" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="D15" s="19" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="F15" s="18" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="G15" s="18" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H15" s="20">
         <x:v>45883.2595717593</x:v>
       </x:c>
-      <x:c r="I15" s="18">
+      <x:c r="I15" s="21">
         <x:v>45101</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="n">
+      <x:c r="J15" s="19" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K15" s="19" t="n">
+      <x:c r="K15" s="22" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L15" s="20">
+      <x:c r="L15" s="23">
         <x:v>45883.2880208333</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M15" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="21" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="23" t="s"/>
-      <x:c r="F18" s="23" t="s"/>
+      <x:c r="B18" s="24" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="26" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="24" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C19" s="25" t="s"/>
-      <x:c r="D19" s="25" t="s"/>
-      <x:c r="E19" s="25" t="s"/>
-      <x:c r="F19" s="26" t="s">
+      <x:c r="B19" s="27" t="s">
         <x:v>59</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="29" t="n">
+      <x:c r="B20" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="31" t="s"/>
+      <x:c r="D20" s="31" t="s"/>
+      <x:c r="E20" s="31" t="s"/>
+      <x:c r="F20" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="27" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
+      <x:c r="B21" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C21" s="31" t="s"/>
+      <x:c r="D21" s="31" t="s"/>
+      <x:c r="E21" s="31" t="s"/>
+      <x:c r="F21" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="27" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C22" s="28" t="s"/>
-      <x:c r="D22" s="28" t="s"/>
-      <x:c r="E22" s="28" t="s"/>
-      <x:c r="F22" s="29" t="n">
+      <x:c r="B22" s="30" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C22" s="31" t="s"/>
+      <x:c r="D22" s="31" t="s"/>
+      <x:c r="E22" s="31" t="s"/>
+      <x:c r="F22" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="27" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C23" s="28" t="s"/>
-      <x:c r="D23" s="28" t="s"/>
-      <x:c r="E23" s="28" t="s"/>
-      <x:c r="F23" s="29" t="n">
+      <x:c r="B23" s="30" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C23" s="31" t="s"/>
+      <x:c r="D23" s="31" t="s"/>
+      <x:c r="E23" s="31" t="s"/>
+      <x:c r="F23" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="27" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C24" s="28" t="s"/>
-      <x:c r="D24" s="28" t="s"/>
-      <x:c r="E24" s="28" t="s"/>
-      <x:c r="F24" s="29" t="n">
+      <x:c r="B24" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C24" s="31" t="s"/>
+      <x:c r="D24" s="31" t="s"/>
+      <x:c r="E24" s="31" t="s"/>
+      <x:c r="F24" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="27" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C25" s="28" t="s"/>
-      <x:c r="D25" s="28" t="s"/>
-      <x:c r="E25" s="28" t="s"/>
-      <x:c r="F25" s="29" t="n">
+      <x:c r="B25" s="30" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C25" s="31" t="s"/>
+      <x:c r="D25" s="31" t="s"/>
+      <x:c r="E25" s="31" t="s"/>
+      <x:c r="F25" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C26" s="28" t="s"/>
-      <x:c r="D26" s="28" t="s"/>
-      <x:c r="E26" s="28" t="s"/>
-      <x:c r="F26" s="29" t="n">
+      <x:c r="B26" s="30" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C26" s="31" t="s"/>
+      <x:c r="D26" s="31" t="s"/>
+      <x:c r="E26" s="31" t="s"/>
+      <x:c r="F26" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="30" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C27" s="31" t="s"/>
-      <x:c r="D27" s="31" t="s"/>
-      <x:c r="E27" s="31" t="s"/>
-      <x:c r="F27" s="32" t="n">
+      <x:c r="B27" s="33" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C27" s="34" t="s"/>
+      <x:c r="D27" s="34" t="s"/>
+      <x:c r="E27" s="34" t="s"/>
+      <x:c r="F27" s="35" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2500,7 +2554,7 @@
   <x:mergeCells count="13">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
@@ -2551,58 +2605,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -2645,81 +2699,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="F8" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45883.0965162037</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="17">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="J8" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
         <x:v>2592.56</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45930.3001388889</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2738,44 +2792,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="23" t="s"/>
-      <x:c r="F11" s="23" t="s"/>
+      <x:c r="B11" s="24" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C11" s="25" t="s"/>
+      <x:c r="D11" s="25" t="s"/>
+      <x:c r="E11" s="26" t="s"/>
+      <x:c r="F11" s="26" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="s">
+      <x:c r="B12" s="27" t="s">
         <x:v>59</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="s"/>
+      <x:c r="D12" s="28" t="s"/>
+      <x:c r="E12" s="28" t="s"/>
+      <x:c r="F12" s="29" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="n">
+      <x:c r="B13" s="30" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="31" t="s"/>
+      <x:c r="D13" s="31" t="s"/>
+      <x:c r="E13" s="31" t="s"/>
+      <x:c r="F13" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="n">
+      <x:c r="B14" s="33" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C14" s="34" t="s"/>
+      <x:c r="D14" s="34" t="s"/>
+      <x:c r="E14" s="34" t="s"/>
+      <x:c r="F14" s="35" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3762,7 +3816,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
@@ -3807,58 +3861,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -3901,81 +3955,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="D8" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46062.2741666667</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="17">
         <x:v>46075</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1346991</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46077.1029513889</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -3994,44 +4048,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="23" t="s"/>
-      <x:c r="F11" s="23" t="s"/>
+      <x:c r="B11" s="24" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C11" s="25" t="s"/>
+      <x:c r="D11" s="25" t="s"/>
+      <x:c r="E11" s="26" t="s"/>
+      <x:c r="F11" s="26" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="s">
+      <x:c r="B12" s="27" t="s">
         <x:v>59</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="s"/>
+      <x:c r="D12" s="28" t="s"/>
+      <x:c r="E12" s="28" t="s"/>
+      <x:c r="F12" s="29" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="n">
+      <x:c r="B13" s="30" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C13" s="31" t="s"/>
+      <x:c r="D13" s="31" t="s"/>
+      <x:c r="E13" s="31" t="s"/>
+      <x:c r="F13" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="n">
+      <x:c r="B14" s="33" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C14" s="34" t="s"/>
+      <x:c r="D14" s="34" t="s"/>
+      <x:c r="E14" s="34" t="s"/>
+      <x:c r="F14" s="35" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -5018,7 +5072,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -69,6 +69,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station License (NEW)</x:t>
@@ -252,10 +288,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -300,15 +338,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -324,15 +354,8 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -590,26 +613,26 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -619,65 +642,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -708,107 +725,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1037,78 +1038,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
-      <x:c r="N4" s="3" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28">
-      <x:c r="A5" s="4" t="s"/>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1129,7 +1142,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1169,423 +1182,473 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45877.1309490741</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>45877.1309606481</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1346451</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>45877.1897222222</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45897.2409837963</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45681</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1346493</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45897.2777430556</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45880.1214814815</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45882</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1346457</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>45881.1618981482</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>45881.0630902778</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45885</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1346453</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>45881.0887037037</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>45897.2535648148</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>45847</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1346494</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>2490</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>45897.2982407407</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>45874.1403125</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46159</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>1346447</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>4230</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>45874.2281365741</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>45883.1535763889</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>1346468</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>4350</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>45883.2560300926</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>45883.2595717593</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>45101</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1346470</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>45883.2880208333</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="20" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C20" s="21" t="s"/>
+      <x:c r="D20" s="21" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="22" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="23" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C21" s="24" t="s"/>
+      <x:c r="D21" s="24" t="s"/>
+      <x:c r="E21" s="24" t="s"/>
+      <x:c r="F21" s="25" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45897.2409837963</x:v>
-      </x:c>
-      <x:c r="I9" s="17">
-        <x:v>45681</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1346493</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45897.2777430556</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="18" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D10" s="19" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E10" s="18" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G10" s="18" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="20">
-        <x:v>45880.1214814815</x:v>
-      </x:c>
-      <x:c r="I10" s="21">
-        <x:v>45882</x:v>
-      </x:c>
-      <x:c r="J10" s="19" t="n">
-        <x:v>1346457</x:v>
-      </x:c>
-      <x:c r="K10" s="22" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L10" s="23">
-        <x:v>45881.1618981482</x:v>
-      </x:c>
-      <x:c r="M10" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s">
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D11" s="19" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F11" s="18" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G11" s="18" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H11" s="20">
-        <x:v>45881.0630902778</x:v>
-      </x:c>
-      <x:c r="I11" s="21">
-        <x:v>45885</x:v>
-      </x:c>
-      <x:c r="J11" s="19" t="n">
-        <x:v>1346453</x:v>
-      </x:c>
-      <x:c r="K11" s="22" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L11" s="23">
-        <x:v>45881.0887037037</x:v>
-      </x:c>
-      <x:c r="M11" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D12" s="19" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E12" s="18" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F12" s="18" t="s">
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="26" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G12" s="18" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H12" s="20">
-        <x:v>45897.2535648148</x:v>
-      </x:c>
-      <x:c r="I12" s="21">
-        <x:v>45847</x:v>
-      </x:c>
-      <x:c r="J12" s="19" t="n">
-        <x:v>1346494</x:v>
-      </x:c>
-      <x:c r="K12" s="22" t="n">
-        <x:v>2490</x:v>
-      </x:c>
-      <x:c r="L12" s="23">
-        <x:v>45897.2982407407</x:v>
-      </x:c>
-      <x:c r="M12" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D13" s="19" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="s">
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="26" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F13" s="18" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G13" s="18" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H13" s="20">
-        <x:v>45874.1403125</x:v>
-      </x:c>
-      <x:c r="I13" s="21">
-        <x:v>46159</x:v>
-      </x:c>
-      <x:c r="J13" s="19" t="n">
-        <x:v>1346447</x:v>
-      </x:c>
-      <x:c r="K13" s="22" t="n">
-        <x:v>4230</x:v>
-      </x:c>
-      <x:c r="L13" s="23">
-        <x:v>45874.2281365741</x:v>
-      </x:c>
-      <x:c r="M13" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="18" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C14" s="18" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D14" s="19" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E14" s="18" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F14" s="18" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G14" s="18" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H14" s="20">
-        <x:v>45883.1535763889</x:v>
-      </x:c>
-      <x:c r="I14" s="21">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J14" s="19" t="n">
-        <x:v>1346468</x:v>
-      </x:c>
-      <x:c r="K14" s="22" t="n">
-        <x:v>4350</x:v>
-      </x:c>
-      <x:c r="L14" s="23">
-        <x:v>45883.2560300926</x:v>
-      </x:c>
-      <x:c r="M14" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="18" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C15" s="18" t="s">
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="26" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D15" s="19" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F15" s="18" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G15" s="18" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H15" s="20">
-        <x:v>45883.2595717593</x:v>
-      </x:c>
-      <x:c r="I15" s="21">
-        <x:v>45101</x:v>
-      </x:c>
-      <x:c r="J15" s="19" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K15" s="22" t="n">
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="L15" s="23">
-        <x:v>45883.2880208333</x:v>
-      </x:c>
-      <x:c r="M15" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="24" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="26" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="s">
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="26" t="s">
         <x:v>60</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="30" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="31" t="s"/>
-      <x:c r="D20" s="31" t="s"/>
-      <x:c r="E20" s="31" t="s"/>
-      <x:c r="F20" s="32" t="n">
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="30" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C21" s="31" t="s"/>
-      <x:c r="D21" s="31" t="s"/>
-      <x:c r="E21" s="31" t="s"/>
-      <x:c r="F21" s="32" t="n">
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="26" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="s"/>
+      <x:c r="D28" s="27" t="s"/>
+      <x:c r="E28" s="27" t="s"/>
+      <x:c r="F28" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="30" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C22" s="31" t="s"/>
-      <x:c r="D22" s="31" t="s"/>
-      <x:c r="E22" s="31" t="s"/>
-      <x:c r="F22" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="30" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C23" s="31" t="s"/>
-      <x:c r="D23" s="31" t="s"/>
-      <x:c r="E23" s="31" t="s"/>
-      <x:c r="F23" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="30" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C24" s="31" t="s"/>
-      <x:c r="D24" s="31" t="s"/>
-      <x:c r="E24" s="31" t="s"/>
-      <x:c r="F24" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="30" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C25" s="31" t="s"/>
-      <x:c r="D25" s="31" t="s"/>
-      <x:c r="E25" s="31" t="s"/>
-      <x:c r="F25" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="30" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C26" s="31" t="s"/>
-      <x:c r="D26" s="31" t="s"/>
-      <x:c r="E26" s="31" t="s"/>
-      <x:c r="F26" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="33" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C27" s="34" t="s"/>
-      <x:c r="D27" s="34" t="s"/>
-      <x:c r="E27" s="34" t="s"/>
-      <x:c r="F27" s="35" t="n">
+    <x:row r="29" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B29" s="29" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C29" s="30" t="s"/>
+      <x:c r="D29" s="30" t="s"/>
+      <x:c r="E29" s="30" t="s"/>
+      <x:c r="F29" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2551,13 +2614,12 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="13">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="14">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
@@ -2565,6 +2627,8 @@
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2605,78 +2669,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2697,7 +2773,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2737,104 +2813,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>45883.0965162037</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>2592.56</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45930.3001388889</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45883.0965162037</x:v>
-      </x:c>
-      <x:c r="I8" s="17">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>2592.56</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45930.3001388889</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="24" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C11" s="25" t="s"/>
-      <x:c r="D11" s="25" t="s"/>
-      <x:c r="E11" s="26" t="s"/>
-      <x:c r="F11" s="26" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="27" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s"/>
-      <x:c r="D12" s="28" t="s"/>
-      <x:c r="E12" s="28" t="s"/>
-      <x:c r="F12" s="29" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="30" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C13" s="31" t="s"/>
-      <x:c r="D13" s="31" t="s"/>
-      <x:c r="E13" s="31" t="s"/>
-      <x:c r="F13" s="32" t="n">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="33" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C14" s="34" t="s"/>
-      <x:c r="D14" s="34" t="s"/>
-      <x:c r="E14" s="34" t="s"/>
-      <x:c r="F14" s="35" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3813,14 +3926,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3861,78 +3975,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3953,7 +4079,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3993,104 +4119,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46062.2741666667</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46075</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46077.1029513889</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46062.2741666667</x:v>
-      </x:c>
-      <x:c r="I8" s="17">
-        <x:v>46075</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46077.1029513889</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="24" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C11" s="25" t="s"/>
-      <x:c r="D11" s="25" t="s"/>
-      <x:c r="E11" s="26" t="s"/>
-      <x:c r="F11" s="26" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="27" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s"/>
-      <x:c r="D12" s="28" t="s"/>
-      <x:c r="E12" s="28" t="s"/>
-      <x:c r="F12" s="29" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="30" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C13" s="31" t="s"/>
-      <x:c r="D13" s="31" t="s"/>
-      <x:c r="E13" s="31" t="s"/>
-      <x:c r="F13" s="32" t="n">
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="33" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C14" s="34" t="s"/>
-      <x:c r="D14" s="34" t="s"/>
-      <x:c r="E14" s="34" t="s"/>
-      <x:c r="F14" s="35" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5069,14 +5232,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -69,42 +69,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station License (NEW)</x:t>
@@ -293,7 +257,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -337,14 +301,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -356,6 +312,21 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -613,7 +584,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -621,16 +592,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -642,59 +613,65 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -725,28 +702,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -761,55 +730,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1142,7 +1127,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1182,473 +1167,423 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45877.1309490741</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45877.1309606481</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1346451</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45877.1897222222</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="D9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45897.2409837963</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45681</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346493</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45897.2777430556</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="B10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="C10" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="D10" s="18" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="17" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45877.1309490741</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45877.1309606481</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1346451</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45877.1897222222</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
+      <x:c r="H10" s="19">
+        <x:v>45880.1214814815</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>45882</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1346457</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>45881.1618981482</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="D11" s="18" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="F11" s="17" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="G11" s="17" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45897.2409837963</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45681</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1346493</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45897.2777430556</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
+      <x:c r="H11" s="19">
+        <x:v>45881.0630902778</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>45885</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1346453</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>45881.0887037037</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="G12" s="17" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45880.1214814815</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45882</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1346457</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45881.1618981482</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>33</x:v>
+      <x:c r="H12" s="19">
+        <x:v>45897.2535648148</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>45847</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1346494</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>2490</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>45897.2982407407</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="F13" s="17" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="G13" s="17" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>45881.0630902778</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>45885</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1346453</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45881.0887037037</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>33</x:v>
+      <x:c r="H13" s="19">
+        <x:v>45874.1403125</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46159</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1346447</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>4230</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>45874.2281365741</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="B14" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="F14" s="17" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="G14" s="17" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>45897.2535648148</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>45847</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1346494</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>2490</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>45897.2982407407</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>33</x:v>
+      <x:c r="H14" s="19">
+        <x:v>45883.1535763889</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1346468</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>4350</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>45883.2560300926</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="D15" s="18" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="F15" s="17" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="G15" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="H15" s="19">
+        <x:v>45883.2595717593</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>45101</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1346470</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>45883.2880208333</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="22" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="24" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="25" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H15" s="17">
-        <x:v>45874.1403125</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46159</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1346447</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>4230</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>45874.2281365741</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>33</x:v>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>45883.1535763889</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1346468</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>4350</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>45883.2560300926</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>33</x:v>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>45883.2595717593</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>45101</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>45883.2880208333</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="20" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C20" s="21" t="s"/>
-      <x:c r="D20" s="21" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="22" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="s">
-        <x:v>72</x:v>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="28" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C21" s="29" t="s"/>
+      <x:c r="D21" s="29" t="s"/>
+      <x:c r="E21" s="29" t="s"/>
+      <x:c r="F21" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="B22" s="28" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C22" s="29" t="s"/>
+      <x:c r="D22" s="29" t="s"/>
+      <x:c r="E22" s="29" t="s"/>
+      <x:c r="F22" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>1</x:v>
+      <x:c r="B23" s="28" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="30" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="B24" s="28" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C24" s="29" t="s"/>
+      <x:c r="D24" s="29" t="s"/>
+      <x:c r="E24" s="29" t="s"/>
+      <x:c r="F24" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
-        <x:v>2</x:v>
+      <x:c r="B25" s="28" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C25" s="29" t="s"/>
+      <x:c r="D25" s="29" t="s"/>
+      <x:c r="E25" s="29" t="s"/>
+      <x:c r="F25" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
+      <x:c r="B26" s="28" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
-        <x:v>1</x:v>
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="31" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C27" s="32" t="s"/>
+      <x:c r="D27" s="32" t="s"/>
+      <x:c r="E27" s="32" t="s"/>
+      <x:c r="F27" s="33" t="n">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="29" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C29" s="30" t="s"/>
-      <x:c r="D29" s="30" t="s"/>
-      <x:c r="E29" s="30" t="s"/>
-      <x:c r="F29" s="31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2619,7 +2554,9 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B20:F20"/>
+    <x:mergeCell ref="B18:F18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
@@ -2627,8 +2564,6 @@
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
-    <x:mergeCell ref="B28:E28"/>
-    <x:mergeCell ref="B29:E29"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2740,7 +2675,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2773,7 +2708,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2813,141 +2748,104 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45883.0965162037</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>2592.56</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45930.3001388889</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45883.0965162037</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>2592.56</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45930.3001388889</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="22" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C11" s="23" t="s"/>
+      <x:c r="D11" s="23" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="24" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="25" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C12" s="26" t="s"/>
+      <x:c r="D12" s="26" t="s"/>
+      <x:c r="E12" s="26" t="s"/>
+      <x:c r="F12" s="27" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="28" t="s">
         <x:v>33</x:v>
       </x:c>
+      <x:c r="C13" s="29" t="s"/>
+      <x:c r="D13" s="29" t="s"/>
+      <x:c r="E13" s="29" t="s"/>
+      <x:c r="F13" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="31" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C14" s="32" t="s"/>
+      <x:c r="D14" s="32" t="s"/>
+      <x:c r="E14" s="32" t="s"/>
+      <x:c r="F14" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3931,10 +3829,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -4046,7 +3944,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -4079,7 +3977,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -4119,141 +4017,104 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46062.2741666667</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46075</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46077.1029513889</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46062.2741666667</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46075</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46077.1029513889</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="22" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C11" s="23" t="s"/>
+      <x:c r="D11" s="23" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="24" t="s"/>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="25" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C12" s="26" t="s"/>
+      <x:c r="D12" s="26" t="s"/>
+      <x:c r="E12" s="26" t="s"/>
+      <x:c r="F12" s="27" t="s">
+        <x:v>60</x:v>
+      </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>72</x:v>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="28" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s"/>
+      <x:c r="D13" s="29" t="s"/>
+      <x:c r="E13" s="29" t="s"/>
+      <x:c r="F13" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="31" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C14" s="32" t="s"/>
+      <x:c r="D14" s="32" t="s"/>
+      <x:c r="E14" s="32" t="s"/>
+      <x:c r="F14" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5237,10 +5098,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -89,6 +89,9 @@
     <x:t>61-8-2025-1102</x:t>
   </x:si>
   <x:si>
+    <x:t>1346451</x:t>
+  </x:si>
+  <x:si>
     <x:t>Neil Jon Angeles</x:t>
   </x:si>
   <x:si>
@@ -110,6 +113,9 @@
     <x:t>61-8-2025-1139</x:t>
   </x:si>
   <x:si>
+    <x:t>1346493</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -125,6 +131,9 @@
     <x:t>61-8-2025-1108</x:t>
   </x:si>
   <x:si>
+    <x:t>1346457</x:t>
+  </x:si>
+  <x:si>
     <x:t>Radio Station License (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -140,6 +149,9 @@
     <x:t>61-8-2025-1109</x:t>
   </x:si>
   <x:si>
+    <x:t>1346453</x:t>
+  </x:si>
+  <x:si>
     <x:t>THUNDER BRAVO NETWORK, INC</x:t>
   </x:si>
   <x:si>
@@ -152,6 +164,9 @@
     <x:t>61-8-2025-1140</x:t>
   </x:si>
   <x:si>
+    <x:t>1346494</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ship Station License DOMESTIC Trade (MODIFICATION)</x:t>
   </x:si>
   <x:si>
@@ -170,6 +185,9 @@
     <x:t>61-8-2025-1090</x:t>
   </x:si>
   <x:si>
+    <x:t>1346447</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ship Station License DOMESTIC Trade (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -185,6 +203,9 @@
     <x:t>61-8-2025-1122</x:t>
   </x:si>
   <x:si>
+    <x:t>1346468</x:t>
+  </x:si>
+  <x:si>
     <x:t>Special Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -200,6 +221,9 @@
     <x:t>61-8-2025-1123</x:t>
   </x:si>
   <x:si>
+    <x:t>1346470</x:t>
+  </x:si>
+  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -246,6 +270,9 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1317-596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1346991</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -326,13 +353,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -350,6 +370,13 @@
       <x:sz val="14"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -625,46 +652,46 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -719,6 +746,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -730,72 +761,68 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1175,7 +1202,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
@@ -1187,398 +1214,398 @@
       <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45877.1309490741</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45877.1309606481</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1346451</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="H8" s="16">
+        <x:v>45877.1309514815</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45877.1309607176</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45877.1897222222</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45877.1897291782</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45897.2409947801</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45681</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>45897.2777466898</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45897.2409837963</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45681</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1346493</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45897.2777430556</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="s">
+      <x:c r="D10" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45880.1214814815</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="F10" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45880.121483588</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45882</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1346457</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45881.1618981482</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45881.1619025579</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G11" s="17" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45881.0630902778</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="D11" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45881.0630940972</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>45885</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1346453</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45881.0887037037</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45881.0887125926</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>45897.2535648148</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="B12" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45897.2535684028</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>45847</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1346494</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>2490</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45897.2982407407</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L12" s="18">
+        <x:v>45897.2982517014</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H13" s="19">
-        <x:v>45874.1403125</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="C13" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45874.1403126505</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
         <x:v>46159</x:v>
       </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1346447</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="J13" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>4230</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>45874.2281365741</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L13" s="18">
+        <x:v>45874.2281447685</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>45883.1535763889</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
+      <x:c r="B14" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45883.1535775463</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1346468</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="J14" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>4350</x:v>
       </x:c>
-      <x:c r="L14" s="21">
-        <x:v>45883.2560300926</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L14" s="18">
+        <x:v>45883.2560389931</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>45883.2595717593</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="B15" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>45883.2595720718</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
         <x:v>45101</x:v>
       </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
+      <x:c r="J15" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L15" s="21">
-        <x:v>45883.2880208333</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L15" s="18">
+        <x:v>45883.2880279051</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s"/>
-      <x:c r="D18" s="23" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="24" t="s"/>
+      <x:c r="B18" s="19" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="s"/>
+      <x:c r="D18" s="20" t="s"/>
+      <x:c r="E18" s="21" t="s"/>
+      <x:c r="F18" s="21" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="s">
-        <x:v>60</x:v>
+      <x:c r="B19" s="22" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="s">
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="28" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="28" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C21" s="29" t="s"/>
-      <x:c r="D21" s="29" t="s"/>
-      <x:c r="E21" s="29" t="s"/>
-      <x:c r="F21" s="30" t="n">
+      <x:c r="B21" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="28" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C22" s="29" t="s"/>
-      <x:c r="D22" s="29" t="s"/>
-      <x:c r="E22" s="29" t="s"/>
-      <x:c r="F22" s="30" t="n">
+      <x:c r="B22" s="25" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="28" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C23" s="29" t="s"/>
-      <x:c r="D23" s="29" t="s"/>
-      <x:c r="E23" s="29" t="s"/>
-      <x:c r="F23" s="30" t="n">
+      <x:c r="B23" s="25" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="28" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C24" s="29" t="s"/>
-      <x:c r="D24" s="29" t="s"/>
-      <x:c r="E24" s="29" t="s"/>
-      <x:c r="F24" s="30" t="n">
+      <x:c r="B24" s="25" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="28" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C25" s="29" t="s"/>
-      <x:c r="D25" s="29" t="s"/>
-      <x:c r="E25" s="29" t="s"/>
-      <x:c r="F25" s="30" t="n">
+      <x:c r="B25" s="25" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="28" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C26" s="29" t="s"/>
-      <x:c r="D26" s="29" t="s"/>
-      <x:c r="E26" s="29" t="s"/>
-      <x:c r="F26" s="30" t="n">
+      <x:c r="B26" s="25" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="31" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C27" s="32" t="s"/>
-      <x:c r="D27" s="32" t="s"/>
-      <x:c r="E27" s="32" t="s"/>
-      <x:c r="F27" s="33" t="n">
+      <x:c r="B27" s="28" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="30" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2675,7 +2702,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2750,41 +2777,41 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45883.0965162037</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="B8" s="31" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E8" s="31" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F8" s="31" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G8" s="31" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>45883.0965271296</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="31" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
         <x:v>2592.56</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45930.3001388889</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="32">
+        <x:v>45930.3001440509</x:v>
+      </x:c>
+      <x:c r="M8" s="31" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2803,44 +2830,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s"/>
-      <x:c r="D11" s="23" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="24" t="s"/>
+      <x:c r="B11" s="19" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="25" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C12" s="26" t="s"/>
-      <x:c r="D12" s="26" t="s"/>
-      <x:c r="E12" s="26" t="s"/>
-      <x:c r="F12" s="27" t="s">
-        <x:v>60</x:v>
+      <x:c r="B12" s="22" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s"/>
-      <x:c r="D13" s="29" t="s"/>
-      <x:c r="E13" s="29" t="s"/>
-      <x:c r="F13" s="30" t="n">
+      <x:c r="B13" s="25" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="31" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C14" s="32" t="s"/>
-      <x:c r="D14" s="32" t="s"/>
-      <x:c r="E14" s="32" t="s"/>
-      <x:c r="F14" s="33" t="n">
+      <x:c r="B14" s="28" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3944,7 +3971,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -4019,41 +4046,41 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46062.2741666667</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="B8" s="31" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E8" s="31" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F8" s="31" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G8" s="31" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>46062.2741739236</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
         <x:v>46075</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="31" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46077.1029513889</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="32">
+        <x:v>46077.1029543634</x:v>
+      </x:c>
+      <x:c r="M8" s="31" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -4072,44 +4099,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s"/>
-      <x:c r="D11" s="23" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="24" t="s"/>
+      <x:c r="B11" s="19" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="25" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C12" s="26" t="s"/>
-      <x:c r="D12" s="26" t="s"/>
-      <x:c r="E12" s="26" t="s"/>
-      <x:c r="F12" s="27" t="s">
-        <x:v>60</x:v>
+      <x:c r="B12" s="22" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s"/>
-      <x:c r="D13" s="29" t="s"/>
-      <x:c r="E13" s="29" t="s"/>
-      <x:c r="F13" s="30" t="n">
+      <x:c r="B13" s="25" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="31" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C14" s="32" t="s"/>
-      <x:c r="D14" s="32" t="s"/>
-      <x:c r="E14" s="32" t="s"/>
-      <x:c r="F14" s="33" t="n">
+      <x:c r="B14" s="28" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -1154,7 +1154,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1194,7 +1194,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1233,7 +1233,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1271,7 +1271,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
@@ -1309,7 +1309,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
@@ -1347,7 +1347,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
@@ -1385,7 +1385,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
@@ -1423,7 +1423,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -1461,7 +1461,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
@@ -2735,7 +2735,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2775,7 +2775,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="31" t="s">
         <x:v>36</x:v>
@@ -4004,7 +4004,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -4044,7 +4044,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="31" t="s">
         <x:v>77</x:v>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>MA. ANNA SOMOZA</x:t>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -32,9 +32,6 @@
     <x:t>MA. ANNA SOMOZA</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | August 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -236,9 +233,6 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | September 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>PETRON CORPORATION - ZAMBOANGA TERMINAL</x:t>
   </x:si>
   <x:si>
@@ -252,9 +246,6 @@
   </x:si>
   <x:si>
     <x:t>1346650/1346651/1346652</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IX | February 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -611,7 +602,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -628,6 +619,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -698,7 +692,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -734,6 +728,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1120,20 +1118,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45870</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1156,456 +1154,456 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45877.1309514815</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45877.1309607176</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45877.1309514815</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45877.1309607176</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45877.1897291782</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45877.1897291782</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
+      <x:c r="E9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45897.2409947801</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45681</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45897.2409947801</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45681</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>45897.2777466898</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45880.121483588</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45882</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45880.121483588</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45882</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45881.1619025579</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>45881.0630940972</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45885</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45881.0630940972</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45885</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>45881.0887125926</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="F12" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="H12" s="17">
+        <x:v>45897.2535684028</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45847</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45897.2535684028</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45847</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>2490</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="19">
         <x:v>45897.2982517014</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="B13" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="D13" s="16" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
+      <x:c r="E13" s="15" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="H13" s="17">
+        <x:v>45874.1403126505</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46159</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45874.1403126505</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46159</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>4230</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="19">
         <x:v>45874.2281447685</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
+      <x:c r="B14" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="D14" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="F14" s="15" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="H14" s="17">
+        <x:v>45883.1535775463</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45883.1535775463</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>4350</x:v>
       </x:c>
-      <x:c r="L14" s="18">
+      <x:c r="L14" s="19">
         <x:v>45883.2560389931</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M14" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
+      <x:c r="B15" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="D15" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="F15" s="15" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="15" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="H15" s="17">
+        <x:v>45883.2595720718</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>45101</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>45883.2595720718</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>45101</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L15" s="18">
+      <x:c r="L15" s="19">
         <x:v>45883.2880279051</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M15" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="19" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C18" s="20" t="s"/>
-      <x:c r="D18" s="20" t="s"/>
-      <x:c r="E18" s="21" t="s"/>
-      <x:c r="F18" s="21" t="s"/>
+      <x:c r="B18" s="20" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="22" t="s">
+      <x:c r="B19" s="23" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s"/>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="24" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
+      <x:c r="B20" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
+      <x:c r="B21" s="26" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
+      <x:c r="B22" s="26" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="25" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="27" t="n">
+      <x:c r="B23" s="26" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="25" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C24" s="26" t="s"/>
-      <x:c r="D24" s="26" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="27" t="n">
+      <x:c r="B24" s="26" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="25" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C25" s="26" t="s"/>
-      <x:c r="D25" s="26" t="s"/>
-      <x:c r="E25" s="26" t="s"/>
-      <x:c r="F25" s="27" t="n">
+      <x:c r="B25" s="26" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="25" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C26" s="26" t="s"/>
-      <x:c r="D26" s="26" t="s"/>
-      <x:c r="E26" s="26" t="s"/>
-      <x:c r="F26" s="27" t="n">
+      <x:c r="B26" s="26" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="28" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C27" s="29" t="s"/>
-      <x:c r="D27" s="29" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="30" t="n">
+      <x:c r="B27" s="29" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C27" s="30" t="s"/>
+      <x:c r="D27" s="30" t="s"/>
+      <x:c r="E27" s="30" t="s"/>
+      <x:c r="F27" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2701,20 +2699,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45901</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2737,81 +2735,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="31" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C8" s="31" t="s">
+      <x:c r="B8" s="32" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C8" s="32" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E8" s="32" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F8" s="32" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E8" s="31" t="s">
+      <x:c r="G8" s="32" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="F8" s="31" t="s">
+      <x:c r="H8" s="33">
+        <x:v>45883.0965271296</x:v>
+      </x:c>
+      <x:c r="I8" s="33">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="J8" s="32" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G8" s="31" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H8" s="32">
-        <x:v>45883.0965271296</x:v>
-      </x:c>
-      <x:c r="I8" s="32">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="J8" s="31" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="34" t="n">
         <x:v>2592.56</x:v>
       </x:c>
-      <x:c r="L8" s="32">
+      <x:c r="L8" s="33">
         <x:v>45930.3001440509</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="32" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2830,44 +2828,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="19" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C11" s="20" t="s"/>
-      <x:c r="D11" s="20" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="21" t="s"/>
+      <x:c r="B11" s="20" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s"/>
+      <x:c r="D11" s="21" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="22" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="22" t="s">
+      <x:c r="B12" s="23" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="24" t="s"/>
+      <x:c r="F12" s="25" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s"/>
-      <x:c r="D12" s="23" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="24" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="25" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="27" t="n">
+      <x:c r="B13" s="26" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="30" t="n">
+      <x:c r="B14" s="29" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3970,20 +3968,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4006,81 +4004,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="31" t="s">
+      <x:c r="B8" s="32" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C8" s="32" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E8" s="32" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F8" s="32" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C8" s="31" t="s">
+      <x:c r="G8" s="32" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E8" s="31" t="s">
+      <x:c r="H8" s="33">
+        <x:v>46062.2741739236</x:v>
+      </x:c>
+      <x:c r="I8" s="33">
+        <x:v>46075</x:v>
+      </x:c>
+      <x:c r="J8" s="32" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="F8" s="31" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G8" s="31" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H8" s="32">
-        <x:v>46062.2741739236</x:v>
-      </x:c>
-      <x:c r="I8" s="32">
-        <x:v>46075</x:v>
-      </x:c>
-      <x:c r="J8" s="31" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="34" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="32">
+      <x:c r="L8" s="33">
         <x:v>46077.1029543634</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="32" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -4099,44 +4097,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="19" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C11" s="20" t="s"/>
-      <x:c r="D11" s="20" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="21" t="s"/>
+      <x:c r="B11" s="20" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s"/>
+      <x:c r="D11" s="21" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="22" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="22" t="s">
+      <x:c r="B12" s="23" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="24" t="s"/>
+      <x:c r="F12" s="25" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s"/>
-      <x:c r="D12" s="23" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="24" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="25" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="27" t="n">
+      <x:c r="B13" s="26" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="30" t="n">
+      <x:c r="B14" s="29" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MA-ANNA-SOMOZA-evaluator-cache-serviceTracking-MA-ANNA-SOMOZA-IX-202501-202612.xlsx
@@ -275,7 +275,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -315,14 +315,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -602,7 +594,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -613,16 +605,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -634,65 +623,65 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -727,99 +716,95 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1121,17 +1106,17 @@
       <x:c r="B5" s="12">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1154,456 +1139,456 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45877.1309514815</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45877.1309607176</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45877.1897291782</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45897.2409947801</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45681</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45897.2777466898</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45880.121483588</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45882</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45881.1619025579</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45881.0630940972</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45885</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45881.0887125926</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45897.2535684028</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45847</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>2490</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45897.2982517014</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45874.1403126505</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46159</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>4230</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45874.2281447685</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>45883.1535775463</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>4350</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>45883.2560389931</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>45883.2595720718</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>45101</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>45883.2880279051</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
+      <x:c r="B18" s="19" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
+      <x:c r="C18" s="20" t="s"/>
+      <x:c r="D18" s="20" t="s"/>
+      <x:c r="E18" s="21" t="s"/>
+      <x:c r="F18" s="21" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="s">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+      <x:c r="B23" s="25" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+      <x:c r="B24" s="25" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
+      <x:c r="B25" s="25" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
+      <x:c r="B26" s="25" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="29" t="s">
+      <x:c r="B27" s="28" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="30" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2702,17 +2687,17 @@
       <x:c r="B5" s="12">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2735,80 +2720,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="32" t="s">
+      <x:c r="B8" s="31" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="s">
+      <x:c r="C8" s="31" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D8" s="32" t="s">
+      <x:c r="D8" s="31" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E8" s="32" t="s">
+      <x:c r="E8" s="31" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F8" s="32" t="s">
+      <x:c r="F8" s="31" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G8" s="32" t="s">
+      <x:c r="G8" s="31" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H8" s="33">
+      <x:c r="H8" s="32">
         <x:v>45883.0965271296</x:v>
       </x:c>
-      <x:c r="I8" s="33">
+      <x:c r="I8" s="32">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="J8" s="32" t="s">
+      <x:c r="J8" s="31" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K8" s="34" t="n">
+      <x:c r="K8" s="33" t="n">
         <x:v>2592.56</x:v>
       </x:c>
-      <x:c r="L8" s="33">
+      <x:c r="L8" s="32">
         <x:v>45930.3001440509</x:v>
       </x:c>
-      <x:c r="M8" s="32" t="s">
+      <x:c r="M8" s="31" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2828,44 +2813,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="20" t="s">
+      <x:c r="B11" s="19" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="22" t="s"/>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="23" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="s">
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+      <x:c r="B13" s="25" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3971,17 +3956,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4004,80 +3989,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="32" t="s">
+      <x:c r="B8" s="31" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="s">
+      <x:c r="C8" s="31" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D8" s="32" t="s">
+      <x:c r="D8" s="31" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E8" s="32" t="s">
+      <x:c r="E8" s="31" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F8" s="32" t="s">
+      <x:c r="F8" s="31" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G8" s="32" t="s">
+      <x:c r="G8" s="31" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="H8" s="33">
+      <x:c r="H8" s="32">
         <x:v>46062.2741739236</x:v>
       </x:c>
-      <x:c r="I8" s="33">
+      <x:c r="I8" s="32">
         <x:v>46075</x:v>
       </x:c>
-      <x:c r="J8" s="32" t="s">
+      <x:c r="J8" s="31" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="K8" s="34" t="n">
+      <x:c r="K8" s="33" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="33">
+      <x:c r="L8" s="32">
         <x:v>46077.1029543634</x:v>
       </x:c>
-      <x:c r="M8" s="32" t="s">
+      <x:c r="M8" s="31" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -4097,44 +4082,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="20" t="s">
+      <x:c r="B11" s="19" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="22" t="s"/>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="23" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="s">
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+      <x:c r="B13" s="25" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
